--- a/quiz/updated-drill-questions/DRT1.xlsx
+++ b/quiz/updated-drill-questions/DRT1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_5 QUESTION DATABASE\_1 Access Database\Driller's\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\firebrigade\wp-content\plugins\techiquiz\quiz\updated-drill-questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DA44F0-144A-42FA-AB13-EB36580AFD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF988A0-C803-4639-9EC6-FEE3B234BF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8A991981-6124-40E3-8D9C-D67951C41F86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8A991981-6124-40E3-8D9C-D67951C41F86}"/>
   </bookViews>
   <sheets>
     <sheet name="DRT1" sheetId="2" r:id="rId1"/>
@@ -1209,9 +1209,6 @@
     <t>To inject hydraulic fluid during ram operation</t>
   </si>
   <si>
-    <t>Driller's Day 1 Practice Test</t>
-  </si>
-  <si>
     <t>DRT1.1</t>
   </si>
   <si>
@@ -1420,6 +1417,9 @@
   </si>
   <si>
     <t>DRT1.70</t>
+  </si>
+  <si>
+    <t>Driller's Day 1 Practice Test Questions</t>
   </si>
 </sst>
 </file>
@@ -1874,7 +1874,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>394</v>
+        <v>464</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>5</v>
@@ -1906,7 +1906,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>73</v>
@@ -1941,7 +1941,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>78</v>
@@ -1976,7 +1976,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>83</v>
@@ -2011,7 +2011,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>88</v>
@@ -2046,7 +2046,7 @@
         <v>19</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>93</v>
@@ -2081,7 +2081,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>98</v>
@@ -2116,7 +2116,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>103</v>
@@ -2151,7 +2151,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>107</v>
@@ -2186,7 +2186,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>112</v>
@@ -2221,7 +2221,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>113</v>
@@ -2256,7 +2256,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>117</v>
@@ -2291,7 +2291,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>122</v>
@@ -2322,7 +2322,7 @@
         <v>25</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>123</v>
@@ -2357,7 +2357,7 @@
         <v>25</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>128</v>
@@ -2392,7 +2392,7 @@
         <v>28</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>133</v>
@@ -2427,7 +2427,7 @@
         <v>28</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>138</v>
@@ -2462,7 +2462,7 @@
         <v>28</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>143</v>
@@ -2497,7 +2497,7 @@
         <v>29</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>148</v>
@@ -2532,7 +2532,7 @@
         <v>29</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>153</v>
@@ -2567,7 +2567,7 @@
         <v>29</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>157</v>
@@ -2602,7 +2602,7 @@
         <v>30</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>162</v>
@@ -2637,7 +2637,7 @@
         <v>30</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>167</v>
@@ -2672,7 +2672,7 @@
         <v>31</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>172</v>
@@ -2707,7 +2707,7 @@
         <v>31</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>177</v>
@@ -2742,7 +2742,7 @@
         <v>33</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>182</v>
@@ -2777,7 +2777,7 @@
         <v>33</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>187</v>
@@ -2812,7 +2812,7 @@
         <v>33</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>191</v>
@@ -2847,7 +2847,7 @@
         <v>39</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>196</v>
@@ -2882,7 +2882,7 @@
         <v>39</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>201</v>
@@ -2917,7 +2917,7 @@
         <v>39</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>41</v>
@@ -2952,7 +2952,7 @@
         <v>39</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>40</v>
@@ -2987,7 +2987,7 @@
         <v>39</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>213</v>
@@ -3022,7 +3022,7 @@
         <v>39</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>218</v>
@@ -3057,7 +3057,7 @@
         <v>44</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>223</v>
@@ -3092,7 +3092,7 @@
         <v>45</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>228</v>
@@ -3127,7 +3127,7 @@
         <v>45</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>233</v>
@@ -3162,7 +3162,7 @@
         <v>45</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>235</v>
@@ -3197,7 +3197,7 @@
         <v>46</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>240</v>
@@ -3232,7 +3232,7 @@
         <v>47</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>245</v>
@@ -3267,7 +3267,7 @@
         <v>47</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>250</v>
@@ -3302,7 +3302,7 @@
         <v>47</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>255</v>
@@ -3337,7 +3337,7 @@
         <v>48</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>260</v>
@@ -3372,7 +3372,7 @@
         <v>22</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>265</v>
@@ -3407,7 +3407,7 @@
         <v>22</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>52</v>
@@ -3442,7 +3442,7 @@
         <v>54</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F46" s="11" t="s">
         <v>274</v>
@@ -3477,7 +3477,7 @@
         <v>21</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F47" s="11" t="s">
         <v>279</v>
@@ -3512,7 +3512,7 @@
         <v>55</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>284</v>
@@ -3547,7 +3547,7 @@
         <v>56</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>289</v>
@@ -3582,7 +3582,7 @@
         <v>56</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>291</v>
@@ -3617,7 +3617,7 @@
         <v>60</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>296</v>
@@ -3652,7 +3652,7 @@
         <v>60</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>301</v>
@@ -3687,7 +3687,7 @@
         <v>60</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F53" s="11" t="s">
         <v>306</v>
@@ -3722,7 +3722,7 @@
         <v>61</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>311</v>
@@ -3757,7 +3757,7 @@
         <v>62</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F55" s="11" t="s">
         <v>316</v>
@@ -3792,7 +3792,7 @@
         <v>62</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>321</v>
@@ -3827,7 +3827,7 @@
         <v>63</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>326</v>
@@ -3862,7 +3862,7 @@
         <v>50</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>331</v>
@@ -3897,7 +3897,7 @@
         <v>51</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>336</v>
@@ -3932,7 +3932,7 @@
         <v>64</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>341</v>
@@ -3967,7 +3967,7 @@
         <v>65</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>346</v>
@@ -4002,7 +4002,7 @@
         <v>66</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F62" s="12" t="s">
         <v>67</v>
@@ -4037,7 +4037,7 @@
         <v>66</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>355</v>
@@ -4072,7 +4072,7 @@
         <v>68</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>359</v>
@@ -4105,7 +4105,7 @@
         <v>69</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>363</v>
@@ -4140,7 +4140,7 @@
         <v>70</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F66" s="12" t="s">
         <v>365</v>
@@ -4175,7 +4175,7 @@
         <v>71</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>368</v>
@@ -4210,7 +4210,7 @@
         <v>71</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F68" s="12" t="s">
         <v>373</v>
@@ -4245,7 +4245,7 @@
         <v>37</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>378</v>
@@ -4280,7 +4280,7 @@
         <v>72</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>383</v>
@@ -4315,7 +4315,7 @@
         <v>388</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>389</v>

--- a/quiz/updated-drill-questions/DRT1.xlsx
+++ b/quiz/updated-drill-questions/DRT1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\firebrigade\wp-content\plugins\techiquiz\quiz\updated-drill-questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF988A0-C803-4639-9EC6-FEE3B234BF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0BDCB1-9BD2-4590-9E9B-5776B49B8146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8A991981-6124-40E3-8D9C-D67951C41F86}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="466">
   <si>
     <t>Ct</t>
   </si>
@@ -1420,6 +1420,9 @@
   </si>
   <si>
     <t>Driller's Day 1 Practice Test Questions</t>
+  </si>
+  <si>
+    <t>Only Supervisor has authority to shut-in a well</t>
   </si>
 </sst>
 </file>
@@ -4077,18 +4080,20 @@
       <c r="F64" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="G64" s="11"/>
+      <c r="G64" s="11" t="s">
+        <v>361</v>
+      </c>
       <c r="H64" s="11" t="s">
         <v>360</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>361</v>
+        <v>465</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>362</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
